--- a/Informacao-Documentada/Informacao-Documentada-modelo.xlsx
+++ b/Informacao-Documentada/Informacao-Documentada-modelo.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Alterações!$B$1:$K$31</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$O$53</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$O$57</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$O$50</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Externos!$B$1:$L$27</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$46</definedName>
@@ -159,7 +159,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="375">
   <si>
     <t xml:space="preserve">Informação documentada — Como usar esta planilha</t>
   </si>
@@ -896,6 +896,12 @@
     <t xml:space="preserve">Porta da câmara fria</t>
   </si>
   <si>
+    <t xml:space="preserve">Planilha de temperatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR</t>
+  </si>
+  <si>
     <t xml:space="preserve">PR-GES-01</t>
   </si>
   <si>
@@ -920,21 +926,33 @@
     <t xml:space="preserve">Pasta da gerência</t>
   </si>
   <si>
+    <t xml:space="preserve">FR-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registro de não conformidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta da qualidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório de auditoria interna</t>
+  </si>
+  <si>
     <t xml:space="preserve">FR-03</t>
   </si>
   <si>
     <t xml:space="preserve">Ficha de alergênicos</t>
   </si>
   <si>
-    <t xml:space="preserve">FR</t>
-  </si>
-  <si>
     <t xml:space="preserve">Produzir e embalar</t>
   </si>
   <si>
-    <t xml:space="preserve">Ambos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sistema de pedidos</t>
   </si>
   <si>
@@ -998,6 +1016,12 @@
     <t xml:space="preserve">Matriz de riscos do delivery</t>
   </si>
   <si>
+    <t xml:space="preserve">FR-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ata da análise crítica</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT-CAI-01</t>
   </si>
   <si>
@@ -1028,9 +1052,6 @@
     <t xml:space="preserve">Exclusão pelo sistema</t>
   </si>
   <si>
-    <t xml:space="preserve">Planilha de temperatura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Etiqueta de conferência do pedido</t>
   </si>
   <si>
@@ -1064,33 +1085,12 @@
     <t xml:space="preserve">Exclusão</t>
   </si>
   <si>
-    <t xml:space="preserve">Registro de não conformidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pasta da qualidade</t>
-  </si>
-  <si>
     <t xml:space="preserve">Picotar e excluir</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório de auditoria interna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-07</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gerente e dono</t>
   </si>
   <si>
-    <t xml:space="preserve">Ata da análise crítica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FR-08</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dono e gerente</t>
   </si>
   <si>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">Gerente de Suprimentos, com o Coordenador da Qualidade</t>
   </si>
   <si>
-    <t xml:space="preserve">Documentos revistos a cada 24 meses. Formulários e listas, a cada 12.</t>
+    <t xml:space="preserve">Documentos revistos a cada 24 meses. Formulários e listas, a cada 12; a lista de fornecedores homologados, a cada 6, com a avaliação semestral. Registros retidos por 3 anos; os de compra, por 5, pelo prazo fiscal; os contratos, por 10.</t>
   </si>
   <si>
     <t xml:space="preserve">Preparação da auditoria de certificação, decidida na análise crítica de 18/02/2027.</t>
@@ -1885,11 +1885,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="8536986"/>
-        <c:axId val="24779611"/>
+        <c:axId val="22253297"/>
+        <c:axId val="31398265"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="8536986"/>
+        <c:axId val="22253297"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1921,7 +1921,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24779611"/>
+        <c:crossAx val="31398265"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1929,7 +1929,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="24779611"/>
+        <c:axId val="31398265"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1969,7 +1969,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8536986"/>
+        <c:crossAx val="22253297"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2063,7 +2063,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Exemplo 1 - Pizzaria'!$B$27:$B$33</c:f>
+              <c:f>'Exemplo 1 - Pizzaria'!$B$31:$B$37</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -2092,12 +2092,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Exemplo 1 - Pizzaria'!$E$27:$E$33</c:f>
+              <c:f>'Exemplo 1 - Pizzaria'!$E$31:$E$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>8</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2123,11 +2123,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="77741406"/>
-        <c:axId val="48340755"/>
+        <c:axId val="5585538"/>
+        <c:axId val="28288535"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="77741406"/>
+        <c:axId val="5585538"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2159,7 +2159,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48340755"/>
+        <c:crossAx val="28288535"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2167,7 +2167,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48340755"/>
+        <c:axId val="28288535"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2207,7 +2207,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77741406"/>
+        <c:crossAx val="5585538"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2361,11 +2361,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="72608930"/>
-        <c:axId val="44893169"/>
+        <c:axId val="29000392"/>
+        <c:axId val="97056100"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="72608930"/>
+        <c:axId val="29000392"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2397,7 +2397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44893169"/>
+        <c:crossAx val="97056100"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2405,7 +2405,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44893169"/>
+        <c:axId val="97056100"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2445,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72608930"/>
+        <c:crossAx val="29000392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2515,13 +2515,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>1326600</xdr:colOff>
-      <xdr:row>34</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>165960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -2530,7 +2530,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="5074920" y="7867800"/>
+        <a:off x="5074920" y="9258480"/>
         <a:ext cx="6119640" cy="2375640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -6372,7 +6372,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:O53"/>
+  <dimension ref="B1:O57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -6607,7 +6607,7 @@
         <v>231</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>46213</v>
+        <v>46280</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>232</v>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="M12" s="17" t="n">
         <f aca="false">IF(OR(G12="",C12=""),"",EDATE(G12,IF(L12="",24,L12)))</f>
-        <v>46944</v>
+        <v>47011</v>
       </c>
       <c r="N12" s="32" t="s">
         <v>106</v>
@@ -6766,43 +6766,43 @@
         <v>Vigente</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="D16" s="32" t="s">
-        <v>247</v>
-      </c>
       <c r="E16" s="7" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="F16" s="33" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="G16" s="34" t="n">
-        <v>46309</v>
+        <v>46295</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>250</v>
-      </c>
       <c r="J16" s="32" t="s">
-        <v>251</v>
+        <v>141</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="L16" s="32" t="n">
         <v>24</v>
       </c>
       <c r="M16" s="17" t="n">
         <f aca="false">IF(OR(G16="",C16=""),"",EDATE(G16,IF(L16="",24,L16)))</f>
-        <v>47040</v>
+        <v>47026</v>
       </c>
       <c r="N16" s="32" t="s">
         <v>106</v>
@@ -6814,41 +6814,41 @@
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>251</v>
+      </c>
+      <c r="G17" s="34" t="n">
+        <v>46309</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J17" s="32" t="s">
         <v>253</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="K17" s="7" t="s">
         <v>254</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="G17" s="34" t="n">
-        <v>46311</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>257</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>258</v>
       </c>
       <c r="L17" s="32" t="n">
         <v>24</v>
       </c>
       <c r="M17" s="17" t="n">
         <f aca="false">IF(OR(G17="",C17=""),"",EDATE(G17,IF(L17="",24,L17)))</f>
-        <v>47042</v>
+        <v>47040</v>
       </c>
       <c r="N17" s="32" t="s">
         <v>106</v>
@@ -6859,124 +6859,134 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="30"/>
+      <c r="B18" s="30" t="s">
+        <v>255</v>
+      </c>
       <c r="C18" s="31" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="34"/>
+        <v>250</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G18" s="34" t="n">
+        <v>46315</v>
+      </c>
       <c r="H18" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="I18" s="7"/>
+        <v>233</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>252</v>
+      </c>
       <c r="J18" s="32" t="s">
-        <v>141</v>
+        <v>257</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="L18" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="M18" s="17" t="str">
+      <c r="M18" s="17" t="n">
         <f aca="false">IF(OR(G18="",C18=""),"",EDATE(G18,IF(L18="",24,L18)))</f>
-        <v/>
+        <v>47046</v>
       </c>
       <c r="N18" s="32" t="s">
         <v>106</v>
       </c>
       <c r="O18" s="18" t="str">
         <f aca="false">IF(C18="","",IF(B18="","Falta o código",IF(N18="Obsoleto","Obsoleto",IF(OR(F18="",G18=""),"Falta a revisão",IF(I18="","Falta a aprovação",IF(N18="Em revisão","Em revisão",IF(M18&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
-        <v>Falta o código</v>
+        <v>Vigente</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="30"/>
+      <c r="B19" s="30" t="s">
+        <v>259</v>
+      </c>
       <c r="C19" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="G19" s="34" t="n">
-        <v>46204</v>
+        <v>46315</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>233</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J19" s="32" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="L19" s="32" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M19" s="17" t="n">
         <f aca="false">IF(OR(G19="",C19=""),"",EDATE(G19,IF(L19="",24,L19)))</f>
-        <v>46569</v>
+        <v>47046</v>
       </c>
       <c r="N19" s="32" t="s">
         <v>106</v>
       </c>
       <c r="O19" s="18" t="str">
         <f aca="false">IF(C19="","",IF(B19="","Falta o código",IF(N19="Obsoleto","Obsoleto",IF(OR(F19="",G19=""),"Falta a revisão",IF(I19="","Falta a aprovação",IF(N19="Em revisão","Em revisão",IF(M19&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
-        <v>Falta o código</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>Vigente</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="30" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>138</v>
+        <v>263</v>
       </c>
       <c r="F20" s="33" t="s">
         <v>243</v>
       </c>
       <c r="G20" s="34" t="n">
-        <v>46237</v>
+        <v>46311</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>233</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L20" s="32" t="n">
         <v>24</v>
       </c>
       <c r="M20" s="17" t="n">
         <f aca="false">IF(OR(G20="",C20=""),"",EDATE(G20,IF(L20="",24,L20)))</f>
-        <v>46968</v>
+        <v>47042</v>
       </c>
       <c r="N20" s="32" t="s">
         <v>106</v>
@@ -6987,132 +6997,124 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="30" t="s">
-        <v>269</v>
-      </c>
+      <c r="B21" s="30"/>
       <c r="C21" s="31" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="G21" s="34" t="n">
-        <v>46213</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="F21" s="33"/>
+      <c r="G21" s="34"/>
       <c r="H21" s="7" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="32" t="s">
         <v>141</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="L21" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="M21" s="17" t="n">
+      <c r="M21" s="17" t="str">
         <f aca="false">IF(OR(G21="",C21=""),"",EDATE(G21,IF(L21="",24,L21)))</f>
-        <v>46944</v>
+        <v/>
       </c>
       <c r="N21" s="32" t="s">
         <v>106</v>
       </c>
       <c r="O21" s="18" t="str">
         <f aca="false">IF(C21="","",IF(B21="","Falta o código",IF(N21="Obsoleto","Obsoleto",IF(OR(F21="",G21=""),"Falta a revisão",IF(I21="","Falta a aprovação",IF(N21="Em revisão","Em revisão",IF(M21&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
-        <v>Falta a aprovação</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="30" t="s">
-        <v>273</v>
-      </c>
+        <v>Falta o código</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="30"/>
       <c r="C22" s="31" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="G22" s="34" t="n">
-        <v>46309</v>
+        <v>46204</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>233</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J22" s="32" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="L22" s="32" t="n">
         <v>12</v>
       </c>
       <c r="M22" s="17" t="n">
         <f aca="false">IF(OR(G22="",C22=""),"",EDATE(G22,IF(L22="",24,L22)))</f>
-        <v>46674</v>
+        <v>46569</v>
       </c>
       <c r="N22" s="32" t="s">
         <v>106</v>
       </c>
       <c r="O22" s="18" t="str">
         <f aca="false">IF(C22="","",IF(B22="","Falta o código",IF(N22="Obsoleto","Obsoleto",IF(OR(F22="",G22=""),"Falta a revisão",IF(I22="","Falta a aprovação",IF(N22="Em revisão","Em revisão",IF(M22&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
-        <v>Vigente</v>
+        <v>Falta o código</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="30" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>276</v>
+        <v>138</v>
       </c>
       <c r="F23" s="33" t="s">
         <v>243</v>
       </c>
       <c r="G23" s="34" t="n">
-        <v>46300</v>
+        <v>46237</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>233</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="L23" s="32" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M23" s="17" t="n">
         <f aca="false">IF(OR(G23="",C23=""),"",EDATE(G23,IF(L23="",24,L23)))</f>
-        <v>46482</v>
+        <v>46968</v>
       </c>
       <c r="N23" s="32" t="s">
         <v>106</v>
@@ -7124,540 +7126,722 @@
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="30" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="F24" s="33" t="s">
         <v>243</v>
       </c>
       <c r="G24" s="34" t="n">
-        <v>45728</v>
+        <v>46213</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="I24" s="7" t="s">
-        <v>250</v>
-      </c>
+      <c r="I24" s="7"/>
       <c r="J24" s="32" t="s">
         <v>141</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="L24" s="32" t="n">
         <v>24</v>
       </c>
       <c r="M24" s="17" t="n">
         <f aca="false">IF(OR(G24="",C24=""),"",EDATE(G24,IF(L24="",24,L24)))</f>
-        <v>46458</v>
+        <v>46944</v>
       </c>
       <c r="N24" s="32" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="O24" s="18" t="str">
         <f aca="false">IF(C24="","",IF(B24="","Falta o código",IF(N24="Obsoleto","Obsoleto",IF(OR(F24="",G24=""),"Falta a revisão",IF(I24="","Falta a aprovação",IF(N24="Em revisão","Em revisão",IF(M24&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
+        <v>Falta a aprovação</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G25" s="34" t="n">
+        <v>46309</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J25" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L25" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <f aca="false">IF(OR(G25="",C25=""),"",EDATE(G25,IF(L25="",24,L25)))</f>
+        <v>46674</v>
+      </c>
+      <c r="N25" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="O25" s="18" t="str">
+        <f aca="false">IF(C25="","",IF(B25="","Falta o código",IF(N25="Obsoleto","Obsoleto",IF(OR(F25="",G25=""),"Falta a revisão",IF(I25="","Falta a aprovação",IF(N25="Em revisão","Em revisão",IF(M25&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
+        <v>Vigente</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>284</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>281</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>46300</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J26" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <f aca="false">IF(OR(G26="",C26=""),"",EDATE(G26,IF(L26="",24,L26)))</f>
+        <v>46482</v>
+      </c>
+      <c r="N26" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="O26" s="18" t="str">
+        <f aca="false">IF(C26="","",IF(B26="","Falta o código",IF(N26="Obsoleto","Obsoleto",IF(OR(F26="",G26=""),"Falta a revisão",IF(I26="","Falta a aprovação",IF(N26="Em revisão","Em revisão",IF(M26&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
+        <v>Vigente</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G27" s="34" t="n">
+        <v>46357</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J27" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="L27" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="M27" s="17" t="n">
+        <f aca="false">IF(OR(G27="",C27=""),"",EDATE(G27,IF(L27="",24,L27)))</f>
+        <v>47088</v>
+      </c>
+      <c r="N27" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="O27" s="18" t="str">
+        <f aca="false">IF(C27="","",IF(B27="","Falta o código",IF(N27="Obsoleto","Obsoleto",IF(OR(F27="",G27=""),"Falta a revisão",IF(I27="","Falta a aprovação",IF(N27="Em revisão","Em revisão",IF(M27&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
+        <v>Vigente</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="G28" s="34" t="n">
+        <v>45728</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="J28" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="L28" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <f aca="false">IF(OR(G28="",C28=""),"",EDATE(G28,IF(L28="",24,L28)))</f>
+        <v>46458</v>
+      </c>
+      <c r="N28" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="O28" s="18" t="str">
+        <f aca="false">IF(C28="","",IF(B28="","Falta o código",IF(N28="Obsoleto","Obsoleto",IF(OR(F28="",G28=""),"Falta a revisão",IF(I28="","Falta a aprovação",IF(N28="Em revisão","Em revisão",IF(M28&lt;$D$5,"Revisão vencida","Vigente")))))))</f>
         <v>Obsoleto</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19" t="s">
+    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-    </row>
-    <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Vigente")</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Em revisão")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Revisão vencida")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Falta o código")</f>
-        <v>3</v>
-      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="20" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
       <c r="E31" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Falta a revisão")</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(O12:O28,"Vigente")</f>
+        <v>12</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="20" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="C32" s="20"/>
       <c r="D32" s="20"/>
       <c r="E32" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Falta a aprovação")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(O12:O28,"Em revisão")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C33" s="20"/>
       <c r="D33" s="20"/>
       <c r="E33" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Obsoleto")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(O12:O28,"Revisão vencida")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="20" t="s">
-        <v>282</v>
+        <v>112</v>
       </c>
       <c r="C34" s="20"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="22" t="n">
-        <f aca="false">(E27+E28)/(SUM(E27:E33)-E33)</f>
-        <v>0.666666666666667</v>
+      <c r="E34" s="21" t="n">
+        <f aca="false">COUNTIF(O12:O28,"Falta o código")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21" t="n">
+        <f aca="false">COUNTIF(O12:O28,"Falta a revisão")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="21" t="n">
+        <f aca="false">COUNTIF(O12:O28,"Falta a aprovação")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="21" t="n">
+        <f aca="false">COUNTIF(O12:O28,"Obsoleto")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="22" t="n">
+        <f aca="false">(E31+E32)/(SUM(E31:E37)-E37)</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="C37" s="35"/>
-      <c r="D37" s="35"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="35"/>
-      <c r="M37" s="35"/>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35"/>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="21" t="s">
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
+      <c r="O41" s="35"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21" t="s">
+      <c r="C42" s="21"/>
+      <c r="D42" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21" t="s">
+      <c r="E42" s="21"/>
+      <c r="F42" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21" t="s">
+      <c r="G42" s="21"/>
+      <c r="H42" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="I38" s="21" t="s">
+      <c r="I42" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="J38" s="21" t="s">
+      <c r="J42" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="K38" s="21" t="s">
+      <c r="K42" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L42" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="M38" s="21"/>
-      <c r="N38" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="O38" s="21"/>
-    </row>
-    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="J39" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="L39" s="32" t="n">
-        <v>24</v>
-      </c>
-      <c r="M39" s="32"/>
-      <c r="N39" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="O39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="J40" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="L40" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="M40" s="32"/>
-      <c r="N40" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="O40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="7" t="s">
+      <c r="M42" s="21"/>
+      <c r="N42" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7" t="s">
+      <c r="O42" s="21"/>
+    </row>
+    <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="31" t="s">
         <v>292</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="J41" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="K41" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="L41" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" s="32"/>
-      <c r="N41" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="O41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="C42" s="31"/>
-      <c r="D42" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="J42" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="K42" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="L42" s="32" t="n">
-        <v>60</v>
-      </c>
-      <c r="M42" s="32"/>
-      <c r="N42" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="O42" s="7"/>
-    </row>
-    <row r="43" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="31" t="s">
-        <v>297</v>
       </c>
       <c r="C43" s="31"/>
       <c r="D43" s="7" t="s">
-        <v>298</v>
+        <v>264</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="J43" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="L43" s="32" t="n">
         <v>24</v>
       </c>
       <c r="M43" s="32"/>
       <c r="N43" s="7" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="O43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="31" t="s">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="C44" s="31"/>
       <c r="D44" s="7" t="s">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7" t="s">
-        <v>296</v>
+        <v>139</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>303</v>
+        <v>140</v>
       </c>
       <c r="J44" s="32" t="s">
-        <v>257</v>
+        <v>141</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>233</v>
+        <v>142</v>
       </c>
       <c r="L44" s="32" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="M44" s="32"/>
       <c r="N44" s="7" t="s">
-        <v>304</v>
+        <v>143</v>
       </c>
       <c r="O44" s="7"/>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="31" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="7" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J45" s="32" t="s">
-        <v>251</v>
+        <v>141</v>
       </c>
       <c r="K45" s="7" t="s">
-        <v>307</v>
+        <v>232</v>
       </c>
       <c r="L45" s="32" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="M45" s="32"/>
       <c r="N45" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="31" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="C46" s="31"/>
       <c r="D46" s="7" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="E46" s="7"/>
       <c r="F46" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>252</v>
+        <v>278</v>
       </c>
       <c r="J46" s="32" t="s">
-        <v>251</v>
+        <v>141</v>
       </c>
       <c r="K46" s="7" t="s">
-        <v>310</v>
+        <v>233</v>
       </c>
       <c r="L46" s="32" t="n">
         <v>60</v>
       </c>
       <c r="M46" s="32"/>
       <c r="N46" s="7" t="s">
-        <v>300</v>
+        <v>143</v>
       </c>
       <c r="O46" s="7"/>
     </row>
-    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="19" t="s">
+    <row r="47" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="C47" s="31"/>
+      <c r="D47" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G47" s="7"/>
+      <c r="H47" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="J47" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="L47" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="M47" s="32"/>
+      <c r="N47" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="O47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="C48" s="31"/>
+      <c r="D48" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="J48" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="L48" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="M48" s="32"/>
+      <c r="N48" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="O48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" s="31"/>
+      <c r="D49" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="J49" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="L49" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="M49" s="32"/>
+      <c r="N49" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="O49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C50" s="31"/>
+      <c r="D50" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G50" s="7"/>
+      <c r="H50" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="J50" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="L50" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="M50" s="32"/>
+      <c r="N50" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="O50" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="19"/>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19"/>
-      <c r="O48" s="19"/>
-    </row>
-    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="21" t="n">
-        <f aca="false">COUNTA(C12:C24)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20"/>
-      <c r="E50" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Falta*")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="20" t="s">
-        <v>312</v>
-      </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="21" t="n">
-        <f aca="false">COUNTIF(O12:O24,"Revisão vencida")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="21" t="n">
-        <f aca="false">COUNTA(B39:B46)</f>
-        <v>8</v>
-      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
+      <c r="N52" s="19"/>
+      <c r="O52" s="19"/>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="20" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
       <c r="E53" s="21" t="n">
-        <f aca="false">MAX(L39:L46)</f>
+        <f aca="false">COUNTA(C12:C28)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="21" t="n">
+        <f aca="false">COUNTIF(O12:O28,"Falta*")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C55" s="20"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="21" t="n">
+        <f aca="false">COUNTIF(O12:O28,"Revisão vencida")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C56" s="20"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="21" t="n">
+        <f aca="false">COUNTA(B43:B50)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="20"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="21" t="n">
+        <f aca="false">MAX(L43:L50)</f>
         <v>60</v>
       </c>
     </row>
@@ -7676,36 +7860,16 @@
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="D8:O8"/>
     <mergeCell ref="B10:O10"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B30:E30"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B37:O37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B41:O41"/>
     <mergeCell ref="B42:C42"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="F42:G42"/>
@@ -7731,14 +7895,34 @@
     <mergeCell ref="F46:G46"/>
     <mergeCell ref="L46:M46"/>
     <mergeCell ref="N46:O46"/>
-    <mergeCell ref="B48:O48"/>
-    <mergeCell ref="B49:D49"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="B51:D51"/>
-    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="B52:O52"/>
     <mergeCell ref="B53:D53"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
   </mergeCells>
-  <conditionalFormatting sqref="O12:O24">
+  <conditionalFormatting sqref="O12:O28">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>O12="Vigente"</formula>
     </cfRule>
@@ -7763,7 +7947,7 @@
     <oddFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="25" man="true" max="16383" min="0"/>
+    <brk id="29" man="true" max="16383" min="0"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -8001,7 +8185,7 @@
         <v>317</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>318</v>
@@ -8019,7 +8203,7 @@
         <v>191</v>
       </c>
       <c r="J12" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>319</v>
@@ -8053,7 +8237,7 @@
         <v>318</v>
       </c>
       <c r="F13" s="33" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G13" s="34" t="n">
         <v>45981</v>
@@ -8065,7 +8249,7 @@
         <v>191</v>
       </c>
       <c r="J13" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>319</v>
@@ -8093,7 +8277,7 @@
         <v>324</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>318</v>
@@ -8111,7 +8295,7 @@
         <v>190</v>
       </c>
       <c r="J14" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>319</v>
@@ -8139,7 +8323,7 @@
         <v>327</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>318</v>
@@ -8157,7 +8341,7 @@
         <v>191</v>
       </c>
       <c r="J15" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>319</v>
@@ -8231,7 +8415,7 @@
         <v>334</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>318</v>
@@ -8249,7 +8433,7 @@
         <v>190</v>
       </c>
       <c r="J17" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>337</v>
@@ -8277,7 +8461,7 @@
         <v>339</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>318</v>
@@ -8295,7 +8479,7 @@
         <v>190</v>
       </c>
       <c r="J18" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>340</v>
@@ -8323,7 +8507,7 @@
         <v>342</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>330</v>
@@ -8369,7 +8553,7 @@
         <v>345</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>318</v>
@@ -8387,7 +8571,7 @@
         <v>190</v>
       </c>
       <c r="J20" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>340</v>
@@ -8413,7 +8597,7 @@
         <v>347</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>318</v>
@@ -8427,7 +8611,7 @@
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>337</v>
@@ -8534,7 +8718,7 @@
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="20" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
@@ -8591,7 +8775,7 @@
       </c>
       <c r="M35" s="21"/>
       <c r="N35" s="21" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="O35" s="21"/>
     </row>
@@ -8615,7 +8799,7 @@
         <v>337</v>
       </c>
       <c r="J36" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>350</v>
@@ -8649,7 +8833,7 @@
         <v>355</v>
       </c>
       <c r="J37" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>356</v>
@@ -8659,7 +8843,7 @@
       </c>
       <c r="M37" s="32"/>
       <c r="N37" s="7" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="O37" s="7"/>
     </row>
@@ -8683,7 +8867,7 @@
         <v>337</v>
       </c>
       <c r="J38" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>358</v>
@@ -8751,7 +8935,7 @@
         <v>340</v>
       </c>
       <c r="J40" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>363</v>
@@ -8761,7 +8945,7 @@
       </c>
       <c r="M40" s="32"/>
       <c r="N40" s="7" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="O40" s="7"/>
     </row>
@@ -8785,7 +8969,7 @@
         <v>366</v>
       </c>
       <c r="J41" s="32" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>363</v>

--- a/Informacao-Documentada/Informacao-Documentada-modelo.xlsx
+++ b/Informacao-Documentada/Informacao-Documentada-modelo.xlsx
@@ -1885,11 +1885,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="22253297"/>
-        <c:axId val="31398265"/>
+        <c:axId val="16980400"/>
+        <c:axId val="91942106"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="22253297"/>
+        <c:axId val="16980400"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1921,7 +1921,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31398265"/>
+        <c:crossAx val="91942106"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1929,7 +1929,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31398265"/>
+        <c:axId val="91942106"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1969,7 +1969,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22253297"/>
+        <c:crossAx val="16980400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2123,11 +2123,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="5585538"/>
-        <c:axId val="28288535"/>
+        <c:axId val="28604350"/>
+        <c:axId val="90221398"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="5585538"/>
+        <c:axId val="28604350"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2159,7 +2159,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28288535"/>
+        <c:crossAx val="90221398"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2167,7 +2167,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="28288535"/>
+        <c:axId val="90221398"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2207,7 +2207,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5585538"/>
+        <c:crossAx val="28604350"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2361,11 +2361,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="29000392"/>
-        <c:axId val="97056100"/>
+        <c:axId val="23404512"/>
+        <c:axId val="43211056"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29000392"/>
+        <c:axId val="23404512"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2397,7 +2397,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97056100"/>
+        <c:crossAx val="43211056"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2405,7 +2405,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97056100"/>
+        <c:axId val="43211056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2445,7 +2445,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29000392"/>
+        <c:crossAx val="23404512"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -6875,7 +6875,7 @@
         <v>243</v>
       </c>
       <c r="G18" s="34" t="n">
-        <v>46315</v>
+        <v>46266</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>233</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="M18" s="17" t="n">
         <f aca="false">IF(OR(G18="",C18=""),"",EDATE(G18,IF(L18="",24,L18)))</f>
-        <v>47046</v>
+        <v>46997</v>
       </c>
       <c r="N18" s="32" t="s">
         <v>106</v>
@@ -6921,7 +6921,7 @@
         <v>243</v>
       </c>
       <c r="G19" s="34" t="n">
-        <v>46315</v>
+        <v>46266</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>233</v>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="M19" s="17" t="n">
         <f aca="false">IF(OR(G19="",C19=""),"",EDATE(G19,IF(L19="",24,L19)))</f>
-        <v>47046</v>
+        <v>46997</v>
       </c>
       <c r="N19" s="32" t="s">
         <v>106</v>
